--- a/province_gis.xlsx
+++ b/province_gis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,51 @@
           <t>province_code</t>
         </is>
       </c>
+      <c r="G1" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>2024</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +532,51 @@
           <t>26</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>8.214485311123587</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14.28583491656973</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.134769148731134</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.696382959787606</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.412410074280704</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8.206896356091162</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.64459525884634</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.050264563189806</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.291744670133128</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.54889323533869</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.902452670275612</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.113143726403496</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.632069600940893</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.261743186888937</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.3956754102529254</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -515,6 +605,51 @@
           <t>24</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>4.364283725930794</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.788241927779066</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.044366447751012</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.586762073391501</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.6338136286053</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8.221436752469049</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.005748959397023</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.859967448309121</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6.336560380563701</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.656112502403039</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.154721385522141</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10.82202987280308</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8.783381015533761</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6.361651406489788</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.413762232872797</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +678,51 @@
           <t>19</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>15.90338472910628</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20.81830481364848</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.91140597474877</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13.29385639270657</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18.14002575129947</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13.7741343283171</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12.08548768478376</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15.23630942317446</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11.66927351492208</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12.46589437327471</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12.6227240595791</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7.490135207359646</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5.961183144885917</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.478614584145308</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.881660186897745</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,6 +751,51 @@
           <t>20</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>29.03356706241316</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30.05001394123334</v>
+      </c>
+      <c r="I5" t="n">
+        <v>29.00834799207733</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13.75146871659538</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12.58136091129853</v>
+      </c>
+      <c r="L5" t="n">
+        <v>11.97207748174984</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12.12000332465605</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12.45951712521056</v>
+      </c>
+      <c r="O5" t="n">
+        <v>14.21404682274247</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.43608414317965</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>15.23354909761737</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7.574170599567073</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.989257213251258</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6.628284114423814</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.942974531309342</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -599,6 +824,51 @@
           <t>25</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>16.22734262108815</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.36616982127496</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.607273860194665</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10.90517788981389</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.787936841530715</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.325030717589952</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.348555332682928</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.911375945828353</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.882664816787652</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.361889323776712</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.614353416086489</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.981627085454508</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.899102121070797</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.856841698629068</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.370101250999963</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -627,6 +897,51 @@
           <t>13</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>9.613822620513341</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12.08084923202405</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.376687182361</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15.8378847167307</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.637161957660979</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.598562241720671</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.928907460203213</v>
+      </c>
+      <c r="N7" t="n">
+        <v>14.50281199163374</v>
+      </c>
+      <c r="O7" t="n">
+        <v>21.60646129550507</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6.37503289967283</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.916290518630091</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.649379659938566</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8.598342840072602</v>
+      </c>
+      <c r="T7" t="n">
+        <v>12.79279295505636</v>
+      </c>
+      <c r="U7" t="n">
+        <v>10.81691881915634</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -655,6 +970,51 @@
           <t>21</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>13.09349749673657</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13.66433782264116</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.831106871872349</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11.23098246786647</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.45174277147029</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.203275857529079</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.233999291424413</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.447178122707198</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.43671813999472</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.435771198023266</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9.498066783079937</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.163026602886875</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.513582636754464</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.848966879723712</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.824136068311685</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -683,6 +1043,51 @@
           <t>14</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>17.44174637883639</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11.08481589662395</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12.11577331602093</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.3867415264637</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.892728945943066</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.336016115085515</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.64798562868531</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.765496658058909</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.924458682531964</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7.024863183167835</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.484993629374127</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.215726849456803</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.498838533736135</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.587284822186003</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.072888521567755</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -711,6 +1116,51 @@
           <t>11</t>
         </is>
       </c>
+      <c r="G10" t="n">
+        <v>13.63444513450439</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.268500250712052</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12.30595664418419</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.63394769835872</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.93483998755159</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.57170513177038</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12.71471504899215</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12.53317786613072</v>
+      </c>
+      <c r="O10" t="n">
+        <v>13.35907483096931</v>
+      </c>
+      <c r="P10" t="n">
+        <v>13.54052709788554</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>15.0135077602001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>15.23504255022063</v>
+      </c>
+      <c r="S10" t="n">
+        <v>18.58498640439519</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21.07083366762069</v>
+      </c>
+      <c r="U10" t="n">
+        <v>21.84041317275728</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -739,6 +1189,51 @@
           <t>12</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>15.46224642402208</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14.59668941484651</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14.2704773332315</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16.44304130444966</v>
+      </c>
+      <c r="K11" t="n">
+        <v>12.20610196514914</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.06107268699509</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11.23781129415234</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.674067290415031</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.725960539556182</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9.069744401609578</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.98009313704057</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4.183874196183092</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8.011626829464879</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.820645502831047</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5.159826842956684</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -767,6 +1262,51 @@
           <t>17</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>8.813816974730619</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.962109622638234</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.163348530881702</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.273165581775261</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7741648995230374</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7670525609111774</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1132417654991327</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.05362842719167522</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4387370161748747</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.762618467392699</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.717304219798767</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.562033532680399</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.777576338830109</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.15471022417047</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.506479165258153</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -795,6 +1335,51 @@
           <t>27</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>25.65842729733427</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16.23217879671781</v>
+      </c>
+      <c r="I13" t="n">
+        <v>19.99086471190178</v>
+      </c>
+      <c r="J13" t="n">
+        <v>17.84973253293388</v>
+      </c>
+      <c r="K13" t="n">
+        <v>23.33698891901206</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24.87666205627959</v>
+      </c>
+      <c r="M13" t="n">
+        <v>23.7508292862921</v>
+      </c>
+      <c r="N13" t="n">
+        <v>21.34501828226968</v>
+      </c>
+      <c r="O13" t="n">
+        <v>20.40618046196759</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14.36506060209913</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>15.14602580868029</v>
+      </c>
+      <c r="R13" t="n">
+        <v>24.73836452660063</v>
+      </c>
+      <c r="S13" t="n">
+        <v>14.08864827278695</v>
+      </c>
+      <c r="T13" t="n">
+        <v>17.03253647968549</v>
+      </c>
+      <c r="U13" t="n">
+        <v>11.99440297073092</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -823,6 +1408,51 @@
           <t>15</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>20.71425591116886</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10.73406534110862</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.228364276539271</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9.156245013216857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11.85087739889179</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10.06499438250761</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8.98049275908566</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7.027621560907738</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8.350146027536622</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12.4183318171909</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>13.87277481024849</v>
+      </c>
+      <c r="R14" t="n">
+        <v>11.63886327132367</v>
+      </c>
+      <c r="S14" t="n">
+        <v>11.24135829835569</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6.527894088995525</v>
+      </c>
+      <c r="U14" t="n">
+        <v>19.1991058486579</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -851,6 +1481,51 @@
           <t>02</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>18.47254313586624</v>
+      </c>
+      <c r="H15" t="n">
+        <v>21.26791075742956</v>
+      </c>
+      <c r="I15" t="n">
+        <v>14.69944105825197</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11.64749309062878</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12.76801655157946</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.027827595413584</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9.62914108001873</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11.12558325938225</v>
+      </c>
+      <c r="O15" t="n">
+        <v>11.05750874781585</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8.816148930648444</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>11.40998778315736</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14.02940498843768</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15.05218792549612</v>
+      </c>
+      <c r="T15" t="n">
+        <v>16.1978412992272</v>
+      </c>
+      <c r="U15" t="n">
+        <v>15.2532241191985</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -879,6 +1554,51 @@
           <t>00</t>
         </is>
       </c>
+      <c r="G16" t="n">
+        <v>17.56662424557803</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13.16368779888057</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.97469162319131</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.01399826088616</v>
+      </c>
+      <c r="K16" t="n">
+        <v>15.57326421672457</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10.33602513873777</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.4286729534085</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9.047260972531937</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6.468815407503399</v>
+      </c>
+      <c r="P16" t="n">
+        <v>7.325669724445729</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7.262785674825831</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7.937741917005589</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7.667922903524947</v>
+      </c>
+      <c r="T16" t="n">
+        <v>9.169188813981226</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7.740456025029233</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -907,6 +1627,51 @@
           <t>16</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>16.22986864441133</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.359767822242444</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.020870005212266</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.116014175921601</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7.027030090931956</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.677096579360915</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.783415216319405</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.088192242010246</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6.464614866328176</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.099543854495249</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.509614455021046</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.466288131694262</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.266828530957659</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.390720978970417</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.897916457925739</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -935,6 +1700,51 @@
           <t>28</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>17.11901084821293</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17.20833773295264</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14.54488697414247</v>
+      </c>
+      <c r="J18" t="n">
+        <v>13.36260715413119</v>
+      </c>
+      <c r="K18" t="n">
+        <v>11.95948391309266</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7.938153674203694</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.571647572198085</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.402986606050561</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.422845721841824</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10.48325696361492</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>15.68571776209998</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8.433046991604899</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6.848301962094064</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6.758905087390519</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.190644533074132</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -963,6 +1773,51 @@
           <t>29</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>15.54459011616227</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.649666659374938</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.829833788959821</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2341477651362529</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.253244814385872</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.304602777874742</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.281491532451831</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.755071427325531</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6.974617065954404</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.514972916081847</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.115011879719924</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.82287906410811</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.265879891756664</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.549008959904554</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.6401765161723781</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -991,6 +1846,51 @@
           <t>05</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>10.55001218929782</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12.03645290495467</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15.82879218721978</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12.52123300639639</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12.77927385420747</v>
+      </c>
+      <c r="L20" t="n">
+        <v>14.45386158823227</v>
+      </c>
+      <c r="M20" t="n">
+        <v>14.16611086815648</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.59045511890113</v>
+      </c>
+      <c r="O20" t="n">
+        <v>6.256104560421302</v>
+      </c>
+      <c r="P20" t="n">
+        <v>12.34968548160033</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10.73510001447265</v>
+      </c>
+      <c r="R20" t="n">
+        <v>8.306290144319329</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10.16925457807965</v>
+      </c>
+      <c r="T20" t="n">
+        <v>11.00710811480013</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7.221638253077585</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1019,6 +1919,51 @@
           <t>08</t>
         </is>
       </c>
+      <c r="G21" t="n">
+        <v>8.374309068643342</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.602109683055687</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.066570728049099</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.656828665066488</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.251560876684165</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.980574548429114</v>
+      </c>
+      <c r="M21" t="n">
+        <v>19.19853514416969</v>
+      </c>
+      <c r="N21" t="n">
+        <v>19.81279673112052</v>
+      </c>
+      <c r="O21" t="n">
+        <v>22.47693841169259</v>
+      </c>
+      <c r="P21" t="n">
+        <v>19.73235968051396</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>13.31144787351886</v>
+      </c>
+      <c r="R21" t="n">
+        <v>14.20406646948719</v>
+      </c>
+      <c r="S21" t="n">
+        <v>18.8166681483101</v>
+      </c>
+      <c r="T21" t="n">
+        <v>16.3351436255261</v>
+      </c>
+      <c r="U21" t="n">
+        <v>16.67709664859791</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1047,6 +1992,51 @@
           <t>09</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>12.9443305528397</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.004128390020424</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9.203300004151075</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9.586155671439272</v>
+      </c>
+      <c r="K22" t="n">
+        <v>9.780190130151226</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9.634036011904213</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10.39427762200415</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13.2387937717469</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12.56348268222129</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12.61466107656021</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>15.63601233240557</v>
+      </c>
+      <c r="R22" t="n">
+        <v>14.38373493271603</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8.73379122939895</v>
+      </c>
+      <c r="T22" t="n">
+        <v>8.771829657478831</v>
+      </c>
+      <c r="U22" t="n">
+        <v>7.584980110171911</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1075,6 +2065,51 @@
           <t>01</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>16.24323511687749</v>
+      </c>
+      <c r="H23" t="n">
+        <v>14.0027345374162</v>
+      </c>
+      <c r="I23" t="n">
+        <v>13.89402970957715</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11.85687401886255</v>
+      </c>
+      <c r="K23" t="n">
+        <v>14.68631875214007</v>
+      </c>
+      <c r="L23" t="n">
+        <v>16.15421983626184</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13.89730449729396</v>
+      </c>
+      <c r="N23" t="n">
+        <v>14.9101170088044</v>
+      </c>
+      <c r="O23" t="n">
+        <v>13.61130571602486</v>
+      </c>
+      <c r="P23" t="n">
+        <v>12.26756333846978</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>12.11177740365711</v>
+      </c>
+      <c r="R23" t="n">
+        <v>15.98382367716773</v>
+      </c>
+      <c r="S23" t="n">
+        <v>13.89993685458227</v>
+      </c>
+      <c r="T23" t="n">
+        <v>12.11688307035842</v>
+      </c>
+      <c r="U23" t="n">
+        <v>11.5967188117014</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1103,6 +2138,51 @@
           <t>03</t>
         </is>
       </c>
+      <c r="G24" t="n">
+        <v>11.46483687537244</v>
+      </c>
+      <c r="H24" t="n">
+        <v>27.78231060965273</v>
+      </c>
+      <c r="I24" t="n">
+        <v>18.09387508094609</v>
+      </c>
+      <c r="J24" t="n">
+        <v>16.20392251630901</v>
+      </c>
+      <c r="K24" t="n">
+        <v>18.40406686367454</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15.58923722570786</v>
+      </c>
+      <c r="M24" t="n">
+        <v>13.27338346043497</v>
+      </c>
+      <c r="N24" t="n">
+        <v>8.327928219015499</v>
+      </c>
+      <c r="O24" t="n">
+        <v>8.080317139663673</v>
+      </c>
+      <c r="P24" t="n">
+        <v>9.134406641310976</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>11.10687787974955</v>
+      </c>
+      <c r="R24" t="n">
+        <v>9.241883630872646</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9.788437986126137</v>
+      </c>
+      <c r="T24" t="n">
+        <v>9.832529237576342</v>
+      </c>
+      <c r="U24" t="n">
+        <v>9.591606363798812</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1131,6 +2211,51 @@
           <t>04</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>11.70643855500209</v>
+      </c>
+      <c r="H25" t="n">
+        <v>17.43621949399602</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15.95806741043698</v>
+      </c>
+      <c r="J25" t="n">
+        <v>18.43012697712933</v>
+      </c>
+      <c r="K25" t="n">
+        <v>14.62673355942737</v>
+      </c>
+      <c r="L25" t="n">
+        <v>14.383105565941</v>
+      </c>
+      <c r="M25" t="n">
+        <v>22.01535081014253</v>
+      </c>
+      <c r="N25" t="n">
+        <v>23.92953704220179</v>
+      </c>
+      <c r="O25" t="n">
+        <v>20.60021130119941</v>
+      </c>
+      <c r="P25" t="n">
+        <v>15.39940421591108</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>17.32834888558418</v>
+      </c>
+      <c r="R25" t="n">
+        <v>14.75656455142232</v>
+      </c>
+      <c r="S25" t="n">
+        <v>19.01399193863356</v>
+      </c>
+      <c r="T25" t="n">
+        <v>30.50723687635899</v>
+      </c>
+      <c r="U25" t="n">
+        <v>21.56194786816691</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1159,6 +2284,51 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G26" t="n">
+        <v>10.56438346574383</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9.122560584739507</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.312682984461927</v>
+      </c>
+      <c r="J26" t="n">
+        <v>9.841375962643548</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9.425371050427549</v>
+      </c>
+      <c r="L26" t="n">
+        <v>11.41531152655703</v>
+      </c>
+      <c r="M26" t="n">
+        <v>12.37682738921613</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8.856278513747592</v>
+      </c>
+      <c r="O26" t="n">
+        <v>7.198219131339063</v>
+      </c>
+      <c r="P26" t="n">
+        <v>10.68565113017613</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>9.310111841597413</v>
+      </c>
+      <c r="R26" t="n">
+        <v>9.141335789196878</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.781167314657571</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5.180166805084379</v>
+      </c>
+      <c r="U26" t="n">
+        <v>9.393164956025849</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1187,6 +2357,51 @@
           <t>23</t>
         </is>
       </c>
+      <c r="G27" t="n">
+        <v>9.891349133533591</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9.449480791377487</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9.456497210626145</v>
+      </c>
+      <c r="J27" t="n">
+        <v>8.38985288581744</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.123271503477085</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3.659699079832164</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.589167227807831</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.404020067808373</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.786221957728478</v>
+      </c>
+      <c r="P27" t="n">
+        <v>6.049687251521172</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.027112406890445</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4.814340496253664</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.303653725627219</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5.471041247315275</v>
+      </c>
+      <c r="U27" t="n">
+        <v>8.386398963967544</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1215,6 +2430,51 @@
           <t>30</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>17.04599717054467</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.342913795266147</v>
+      </c>
+      <c r="I28" t="n">
+        <v>8.613733377798297</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.13728139727051</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.871840413522068</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.177500407900542</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.632596361394443</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.041378982975756</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.939537282458599</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4.695753062631032</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.732283107980071</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.861699122690416</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5.170760297388713</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4.023803077848864</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.964766092438264</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1243,6 +2503,51 @@
           <t>22</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>10.76005762571984</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.545906156089259</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.411730016435307</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.63998900358331</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8.754258416109478</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7.460887088703498</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.584188055583113</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9.402797410325896</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8.498849953940702</v>
+      </c>
+      <c r="P29" t="n">
+        <v>8.751178244917122</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>16.25123198191224</v>
+      </c>
+      <c r="R29" t="n">
+        <v>16.02228144264672</v>
+      </c>
+      <c r="S29" t="n">
+        <v>12.97272496688859</v>
+      </c>
+      <c r="T29" t="n">
+        <v>11.60333160113212</v>
+      </c>
+      <c r="U29" t="n">
+        <v>11.44583927677233</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1271,6 +2576,51 @@
           <t>18</t>
         </is>
       </c>
+      <c r="G30" t="n">
+        <v>9.630185121083256</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7.288937680649638</v>
+      </c>
+      <c r="I30" t="n">
+        <v>18.75124898564892</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8.041706917918944</v>
+      </c>
+      <c r="K30" t="n">
+        <v>7.835878909742244</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11.80246200560098</v>
+      </c>
+      <c r="M30" t="n">
+        <v>15.29513809129406</v>
+      </c>
+      <c r="N30" t="n">
+        <v>13.08639867160497</v>
+      </c>
+      <c r="O30" t="n">
+        <v>13.35745414241529</v>
+      </c>
+      <c r="P30" t="n">
+        <v>11.94015540035137</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8.860476413419329</v>
+      </c>
+      <c r="R30" t="n">
+        <v>10.01244780996343</v>
+      </c>
+      <c r="S30" t="n">
+        <v>9.283956597649865</v>
+      </c>
+      <c r="T30" t="n">
+        <v>9.419800987075613</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9.843682716661032</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1299,6 +2649,51 @@
           <t>07</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>7.518799174276801</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8.595269865937547</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6.705298756389677</v>
+      </c>
+      <c r="J31" t="n">
+        <v>8.097657845579882</v>
+      </c>
+      <c r="K31" t="n">
+        <v>7.621068184112836</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.08997926771158</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7.312798428429113</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.526354247028796</v>
+      </c>
+      <c r="O31" t="n">
+        <v>5.550755823625056</v>
+      </c>
+      <c r="P31" t="n">
+        <v>7.627650063294405</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7.222542579260595</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7.481592836007287</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9.431995351558733</v>
+      </c>
+      <c r="T31" t="n">
+        <v>8.657815079110083</v>
+      </c>
+      <c r="U31" t="n">
+        <v>7.775896371160044</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1326,6 +2721,51 @@
         <is>
           <t>06</t>
         </is>
+      </c>
+      <c r="G32" t="n">
+        <v>8.475964984255304</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.962112806688133</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.289874548303282</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.072956177904338</v>
+      </c>
+      <c r="K32" t="n">
+        <v>7.044826580058182</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.582440550149951</v>
+      </c>
+      <c r="M32" t="n">
+        <v>6.220779653905655</v>
+      </c>
+      <c r="N32" t="n">
+        <v>9.762708139710561</v>
+      </c>
+      <c r="O32" t="n">
+        <v>10.03272024746781</v>
+      </c>
+      <c r="P32" t="n">
+        <v>5.790886039743818</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7.41004101540194</v>
+      </c>
+      <c r="R32" t="n">
+        <v>5.660272707544835</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6.249444987983808</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.707011878536052</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5.317883520350244</v>
       </c>
     </row>
   </sheetData>

--- a/province_gis.xlsx
+++ b/province_gis.xlsx
@@ -429,2343 +429,2338 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Province_N</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Province_E</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Shape_Length</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Shape_Area</t>
+          <t>province</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>province</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>province_code</t>
         </is>
       </c>
+      <c r="F1" s="1" t="n">
+        <v>2010</v>
+      </c>
       <c r="G1" s="1" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H1" s="1" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="I1" s="1" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="J1" s="1" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="K1" s="1" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="L1" s="1" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="M1" s="1" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="N1" s="1" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="O1" s="1" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="P1" s="1" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="Q1" s="1" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="R1" s="1" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="S1" s="1" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="T1" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="U1" s="1" t="n">
         <v>2024</v>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>share_connected</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>قزوین</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Qazvin</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>748134.0792638517</v>
-      </c>
-      <c r="D2" t="n">
-        <v>15635402270.00144</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Qazvin</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qazvin</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
           <t>26</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>8.214485311123587</v>
+      </c>
       <c r="G2" t="n">
-        <v>8.214485311123587</v>
+        <v>14.28583491656973</v>
       </c>
       <c r="H2" t="n">
-        <v>14.28583491656973</v>
+        <v>8.134769148731134</v>
       </c>
       <c r="I2" t="n">
-        <v>8.134769148731134</v>
+        <v>9.696382959787606</v>
       </c>
       <c r="J2" t="n">
-        <v>9.696382959787606</v>
+        <v>9.412410074280704</v>
       </c>
       <c r="K2" t="n">
-        <v>9.412410074280704</v>
+        <v>8.206896356091162</v>
       </c>
       <c r="L2" t="n">
-        <v>8.206896356091162</v>
+        <v>7.64459525884634</v>
       </c>
       <c r="M2" t="n">
-        <v>7.64459525884634</v>
+        <v>6.050264563189806</v>
       </c>
       <c r="N2" t="n">
-        <v>6.050264563189806</v>
+        <v>4.291744670133128</v>
       </c>
       <c r="O2" t="n">
-        <v>4.291744670133128</v>
+        <v>4.54889323533869</v>
       </c>
       <c r="P2" t="n">
-        <v>4.54889323533869</v>
+        <v>1.902452670275612</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.902452670275612</v>
+        <v>2.113143726403496</v>
       </c>
       <c r="R2" t="n">
-        <v>2.113143726403496</v>
+        <v>1.632069600940893</v>
       </c>
       <c r="S2" t="n">
-        <v>1.632069600940893</v>
+        <v>1.261743186888937</v>
       </c>
       <c r="T2" t="n">
-        <v>1.261743186888937</v>
+        <v>0.3956754102529254</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3956754102529254</v>
+        <v>99.78122766790449</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>اردبیل</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Ardebil</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1042156.476364573</v>
-      </c>
-      <c r="D3" t="n">
-        <v>17999098261.19488</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ardabil</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ardabil</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>24</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>4.364283725930794</v>
+      </c>
       <c r="G3" t="n">
-        <v>4.364283725930794</v>
+        <v>7.788241927779066</v>
       </c>
       <c r="H3" t="n">
-        <v>7.788241927779066</v>
+        <v>7.044366447751012</v>
       </c>
       <c r="I3" t="n">
-        <v>7.044366447751012</v>
+        <v>6.586762073391501</v>
       </c>
       <c r="J3" t="n">
-        <v>6.586762073391501</v>
+        <v>7.6338136286053</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6338136286053</v>
+        <v>8.221436752469049</v>
       </c>
       <c r="L3" t="n">
-        <v>8.221436752469049</v>
+        <v>9.005748959397023</v>
       </c>
       <c r="M3" t="n">
-        <v>9.005748959397023</v>
+        <v>6.859967448309121</v>
       </c>
       <c r="N3" t="n">
-        <v>6.859967448309121</v>
+        <v>6.336560380563701</v>
       </c>
       <c r="O3" t="n">
-        <v>6.336560380563701</v>
+        <v>8.656112502403039</v>
       </c>
       <c r="P3" t="n">
-        <v>8.656112502403039</v>
+        <v>7.154721385522141</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.154721385522141</v>
+        <v>10.82202987280308</v>
       </c>
       <c r="R3" t="n">
-        <v>10.82202987280308</v>
+        <v>8.783381015533761</v>
       </c>
       <c r="S3" t="n">
-        <v>8.783381015533761</v>
+        <v>6.361651406489788</v>
       </c>
       <c r="T3" t="n">
-        <v>6.361651406489788</v>
+        <v>5.413762232872797</v>
       </c>
       <c r="U3" t="n">
-        <v>5.413762232872797</v>
+        <v>99.94614347095882</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>زنجان</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Zanjan</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>803819.8689842391</v>
-      </c>
-      <c r="D4" t="n">
-        <v>21739889247.95922</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Zanjan</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zanjan</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>19</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>15.90338472910628</v>
+      </c>
       <c r="G4" t="n">
-        <v>15.90338472910628</v>
+        <v>20.81830481364848</v>
       </c>
       <c r="H4" t="n">
-        <v>20.81830481364848</v>
+        <v>11.91140597474877</v>
       </c>
       <c r="I4" t="n">
-        <v>11.91140597474877</v>
+        <v>13.29385639270657</v>
       </c>
       <c r="J4" t="n">
-        <v>13.29385639270657</v>
+        <v>18.14002575129947</v>
       </c>
       <c r="K4" t="n">
-        <v>18.14002575129947</v>
+        <v>13.7741343283171</v>
       </c>
       <c r="L4" t="n">
-        <v>13.7741343283171</v>
+        <v>12.08548768478376</v>
       </c>
       <c r="M4" t="n">
-        <v>12.08548768478376</v>
+        <v>15.23630942317446</v>
       </c>
       <c r="N4" t="n">
-        <v>15.23630942317446</v>
+        <v>11.66927351492208</v>
       </c>
       <c r="O4" t="n">
-        <v>11.66927351492208</v>
+        <v>12.46589437327471</v>
       </c>
       <c r="P4" t="n">
-        <v>12.46589437327471</v>
+        <v>12.6227240595791</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.6227240595791</v>
+        <v>7.490135207359646</v>
       </c>
       <c r="R4" t="n">
-        <v>7.490135207359646</v>
+        <v>5.961183144885917</v>
       </c>
       <c r="S4" t="n">
-        <v>5.961183144885917</v>
+        <v>4.478614584145308</v>
       </c>
       <c r="T4" t="n">
-        <v>4.478614584145308</v>
+        <v>3.881660186897745</v>
       </c>
       <c r="U4" t="n">
-        <v>3.881660186897745</v>
+        <v>98.76947300875173</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>سمنان</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Semnan</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1561825.840408988</v>
-      </c>
-      <c r="D5" t="n">
-        <v>97141027649.252</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Semnan</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semnan</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>20</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>29.03356706241316</v>
+      </c>
       <c r="G5" t="n">
-        <v>29.03356706241316</v>
+        <v>30.05001394123334</v>
       </c>
       <c r="H5" t="n">
-        <v>30.05001394123334</v>
+        <v>29.00834799207733</v>
       </c>
       <c r="I5" t="n">
-        <v>29.00834799207733</v>
+        <v>13.75146871659538</v>
       </c>
       <c r="J5" t="n">
-        <v>13.75146871659538</v>
+        <v>12.58136091129853</v>
       </c>
       <c r="K5" t="n">
-        <v>12.58136091129853</v>
+        <v>11.97207748174984</v>
       </c>
       <c r="L5" t="n">
-        <v>11.97207748174984</v>
+        <v>12.12000332465605</v>
       </c>
       <c r="M5" t="n">
-        <v>12.12000332465605</v>
+        <v>12.45951712521056</v>
       </c>
       <c r="N5" t="n">
-        <v>12.45951712521056</v>
+        <v>14.21404682274247</v>
       </c>
       <c r="O5" t="n">
-        <v>14.21404682274247</v>
+        <v>10.43608414317965</v>
       </c>
       <c r="P5" t="n">
-        <v>10.43608414317965</v>
+        <v>15.23354909761737</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.23354909761737</v>
+        <v>7.574170599567073</v>
       </c>
       <c r="R5" t="n">
-        <v>7.574170599567073</v>
+        <v>5.989257213251258</v>
       </c>
       <c r="S5" t="n">
-        <v>5.989257213251258</v>
+        <v>6.628284114423814</v>
       </c>
       <c r="T5" t="n">
-        <v>6.628284114423814</v>
+        <v>4.942974531309342</v>
       </c>
       <c r="U5" t="n">
-        <v>4.942974531309342</v>
+        <v>98.54568750887127</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>قم</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Qom</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>517162.3561617981</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11474220549.15713</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Qom</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qom</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>16.22734262108815</v>
+      </c>
       <c r="G6" t="n">
-        <v>16.22734262108815</v>
+        <v>10.36616982127496</v>
       </c>
       <c r="H6" t="n">
-        <v>10.36616982127496</v>
+        <v>6.607273860194665</v>
       </c>
       <c r="I6" t="n">
-        <v>6.607273860194665</v>
+        <v>10.90517788981389</v>
       </c>
       <c r="J6" t="n">
-        <v>10.90517788981389</v>
+        <v>6.787936841530715</v>
       </c>
       <c r="K6" t="n">
-        <v>6.787936841530715</v>
+        <v>6.325030717589952</v>
       </c>
       <c r="L6" t="n">
-        <v>6.325030717589952</v>
+        <v>2.348555332682928</v>
       </c>
       <c r="M6" t="n">
-        <v>2.348555332682928</v>
+        <v>2.911375945828353</v>
       </c>
       <c r="N6" t="n">
-        <v>2.911375945828353</v>
+        <v>1.882664816787652</v>
       </c>
       <c r="O6" t="n">
-        <v>1.882664816787652</v>
+        <v>3.361889323776712</v>
       </c>
       <c r="P6" t="n">
-        <v>3.361889323776712</v>
+        <v>3.614353416086489</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.614353416086489</v>
+        <v>1.981627085454508</v>
       </c>
       <c r="R6" t="n">
-        <v>1.981627085454508</v>
+        <v>5.899102121070797</v>
       </c>
       <c r="S6" t="n">
-        <v>5.899102121070797</v>
+        <v>2.856841698629068</v>
       </c>
       <c r="T6" t="n">
-        <v>2.856841698629068</v>
+        <v>2.370101250999963</v>
       </c>
       <c r="U6" t="n">
-        <v>2.370101250999963</v>
+        <v>99.92128973313574</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>همدان</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Hamedan</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>861809.7190452642</v>
-      </c>
-      <c r="D7" t="n">
-        <v>19360468570.40825</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hamadan</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hamadan</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>13</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>9.613822620513341</v>
+      </c>
       <c r="G7" t="n">
-        <v>9.613822620513341</v>
+        <v>12.08084923202405</v>
       </c>
       <c r="H7" t="n">
-        <v>12.08084923202405</v>
+        <v>10.376687182361</v>
       </c>
       <c r="I7" t="n">
-        <v>10.376687182361</v>
+        <v>15.8378847167307</v>
       </c>
       <c r="J7" t="n">
-        <v>15.8378847167307</v>
+        <v>9.637161957660979</v>
       </c>
       <c r="K7" t="n">
-        <v>9.637161957660979</v>
+        <v>9.598562241720671</v>
       </c>
       <c r="L7" t="n">
-        <v>9.598562241720671</v>
+        <v>9.928907460203213</v>
       </c>
       <c r="M7" t="n">
-        <v>9.928907460203213</v>
+        <v>14.50281199163374</v>
       </c>
       <c r="N7" t="n">
-        <v>14.50281199163374</v>
+        <v>21.60646129550507</v>
       </c>
       <c r="O7" t="n">
-        <v>21.60646129550507</v>
+        <v>6.37503289967283</v>
       </c>
       <c r="P7" t="n">
-        <v>6.37503289967283</v>
+        <v>4.916290518630091</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.916290518630091</v>
+        <v>5.649379659938566</v>
       </c>
       <c r="R7" t="n">
-        <v>5.649379659938566</v>
+        <v>8.598342840072602</v>
       </c>
       <c r="S7" t="n">
-        <v>8.598342840072602</v>
+        <v>12.79279295505636</v>
       </c>
       <c r="T7" t="n">
-        <v>12.79279295505636</v>
+        <v>10.81691881915634</v>
       </c>
       <c r="U7" t="n">
-        <v>10.81691881915634</v>
+        <v>99.95649268921795</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>یزد</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Yazd</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1389852.793710677</v>
-      </c>
-      <c r="D8" t="n">
-        <v>73628201871.82463</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yazd</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yazd</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>21</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>13.09349749673657</v>
+      </c>
       <c r="G8" t="n">
-        <v>13.09349749673657</v>
+        <v>13.66433782264116</v>
       </c>
       <c r="H8" t="n">
-        <v>13.66433782264116</v>
+        <v>9.831106871872349</v>
       </c>
       <c r="I8" t="n">
-        <v>9.831106871872349</v>
+        <v>11.23098246786647</v>
       </c>
       <c r="J8" t="n">
-        <v>11.23098246786647</v>
+        <v>9.45174277147029</v>
       </c>
       <c r="K8" t="n">
-        <v>9.45174277147029</v>
+        <v>4.203275857529079</v>
       </c>
       <c r="L8" t="n">
-        <v>4.203275857529079</v>
+        <v>3.233999291424413</v>
       </c>
       <c r="M8" t="n">
-        <v>3.233999291424413</v>
+        <v>2.447178122707198</v>
       </c>
       <c r="N8" t="n">
-        <v>2.447178122707198</v>
+        <v>5.43671813999472</v>
       </c>
       <c r="O8" t="n">
-        <v>5.43671813999472</v>
+        <v>7.435771198023266</v>
       </c>
       <c r="P8" t="n">
-        <v>7.435771198023266</v>
+        <v>9.498066783079937</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.498066783079937</v>
+        <v>3.163026602886875</v>
       </c>
       <c r="R8" t="n">
-        <v>3.163026602886875</v>
+        <v>3.513582636754464</v>
       </c>
       <c r="S8" t="n">
-        <v>3.513582636754464</v>
+        <v>5.848966879723712</v>
       </c>
       <c r="T8" t="n">
-        <v>5.848966879723712</v>
+        <v>5.824136068311685</v>
       </c>
       <c r="U8" t="n">
-        <v>5.824136068311685</v>
+        <v>99.80696894157526</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>چهارمحال وبختیاری</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Chaharmahal va Bakhtiyari</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>721212.5187087292</v>
-      </c>
-      <c r="D9" t="n">
-        <v>16301244398.08552</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chaharmahal and Bakhtiari</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chaharmahal and Bakhtiari</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>14</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>17.44174637883639</v>
+      </c>
       <c r="G9" t="n">
-        <v>17.44174637883639</v>
+        <v>11.08481589662395</v>
       </c>
       <c r="H9" t="n">
-        <v>11.08481589662395</v>
+        <v>12.11577331602093</v>
       </c>
       <c r="I9" t="n">
-        <v>12.11577331602093</v>
+        <v>10.3867415264637</v>
       </c>
       <c r="J9" t="n">
-        <v>10.3867415264637</v>
+        <v>8.892728945943066</v>
       </c>
       <c r="K9" t="n">
-        <v>8.892728945943066</v>
+        <v>9.336016115085515</v>
       </c>
       <c r="L9" t="n">
-        <v>9.336016115085515</v>
+        <v>2.64798562868531</v>
       </c>
       <c r="M9" t="n">
-        <v>2.64798562868531</v>
+        <v>2.765496658058909</v>
       </c>
       <c r="N9" t="n">
-        <v>2.765496658058909</v>
+        <v>5.924458682531964</v>
       </c>
       <c r="O9" t="n">
-        <v>5.924458682531964</v>
+        <v>7.024863183167835</v>
       </c>
       <c r="P9" t="n">
-        <v>7.024863183167835</v>
+        <v>3.484993629374127</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.484993629374127</v>
+        <v>1.215726849456803</v>
       </c>
       <c r="R9" t="n">
-        <v>1.215726849456803</v>
+        <v>2.498838533736135</v>
       </c>
       <c r="S9" t="n">
-        <v>2.498838533736135</v>
+        <v>4.587284822186003</v>
       </c>
       <c r="T9" t="n">
-        <v>4.587284822186003</v>
+        <v>3.072888521567755</v>
       </c>
       <c r="U9" t="n">
-        <v>3.072888521567755</v>
+        <v>97.7062207953209</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>سیستان وبلوچستان</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Sistan va Baluchestan</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>2509779.369610838</v>
-      </c>
-      <c r="D10" t="n">
-        <v>178998900807.1392</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sistan and Baluchestan</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sistan and Baluchestan</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t>11</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>13.63444513450439</v>
+      </c>
       <c r="G10" t="n">
-        <v>13.63444513450439</v>
+        <v>7.268500250712052</v>
       </c>
       <c r="H10" t="n">
-        <v>7.268500250712052</v>
+        <v>12.30595664418419</v>
       </c>
       <c r="I10" t="n">
-        <v>12.30595664418419</v>
+        <v>11.63394769835872</v>
       </c>
       <c r="J10" t="n">
-        <v>11.63394769835872</v>
+        <v>11.93483998755159</v>
       </c>
       <c r="K10" t="n">
-        <v>11.93483998755159</v>
+        <v>12.57170513177038</v>
       </c>
       <c r="L10" t="n">
-        <v>12.57170513177038</v>
+        <v>12.71471504899215</v>
       </c>
       <c r="M10" t="n">
-        <v>12.71471504899215</v>
+        <v>12.53317786613072</v>
       </c>
       <c r="N10" t="n">
-        <v>12.53317786613072</v>
+        <v>13.35907483096931</v>
       </c>
       <c r="O10" t="n">
-        <v>13.35907483096931</v>
+        <v>13.54052709788554</v>
       </c>
       <c r="P10" t="n">
-        <v>13.54052709788554</v>
+        <v>15.0135077602001</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.0135077602001</v>
+        <v>15.23504255022063</v>
       </c>
       <c r="R10" t="n">
-        <v>15.23504255022063</v>
+        <v>18.58498640439519</v>
       </c>
       <c r="S10" t="n">
-        <v>18.58498640439519</v>
+        <v>21.07083366762069</v>
       </c>
       <c r="T10" t="n">
-        <v>21.07083366762069</v>
+        <v>21.84041317275728</v>
       </c>
       <c r="U10" t="n">
-        <v>21.84041317275728</v>
+        <v>21.43598237804387</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>کردستان</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Kordestan</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1071041.571445747</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29040489450.19041</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kurdistan</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kurdistan</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>12</t>
         </is>
       </c>
+      <c r="F11" t="n">
+        <v>15.46224642402208</v>
+      </c>
       <c r="G11" t="n">
-        <v>15.46224642402208</v>
+        <v>14.59668941484651</v>
       </c>
       <c r="H11" t="n">
-        <v>14.59668941484651</v>
+        <v>14.2704773332315</v>
       </c>
       <c r="I11" t="n">
-        <v>14.2704773332315</v>
+        <v>16.44304130444966</v>
       </c>
       <c r="J11" t="n">
-        <v>16.44304130444966</v>
+        <v>12.20610196514914</v>
       </c>
       <c r="K11" t="n">
-        <v>12.20610196514914</v>
+        <v>12.06107268699509</v>
       </c>
       <c r="L11" t="n">
-        <v>12.06107268699509</v>
+        <v>11.23781129415234</v>
       </c>
       <c r="M11" t="n">
-        <v>11.23781129415234</v>
+        <v>7.674067290415031</v>
       </c>
       <c r="N11" t="n">
-        <v>7.674067290415031</v>
+        <v>5.725960539556182</v>
       </c>
       <c r="O11" t="n">
-        <v>5.725960539556182</v>
+        <v>9.069744401609578</v>
       </c>
       <c r="P11" t="n">
-        <v>9.069744401609578</v>
+        <v>4.98009313704057</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.98009313704057</v>
+        <v>4.183874196183092</v>
       </c>
       <c r="R11" t="n">
-        <v>4.183874196183092</v>
+        <v>8.011626829464879</v>
       </c>
       <c r="S11" t="n">
-        <v>8.011626829464879</v>
+        <v>5.820645502831047</v>
       </c>
       <c r="T11" t="n">
-        <v>5.820645502831047</v>
+        <v>5.159826842956684</v>
       </c>
       <c r="U11" t="n">
-        <v>5.159826842956684</v>
+        <v>99.63109235343558</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>کهگیلویه وبویراحمد</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Kohgiluyeh va Boyerahmad</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>777516.418628837</v>
-      </c>
-      <c r="D12" t="n">
-        <v>15434187115.88927</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kohgiluyeh and Boyer-Ahmad</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kohgiluyeh and Boyer-Ahmad</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>17</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>8.813816974730619</v>
+      </c>
       <c r="G12" t="n">
-        <v>8.813816974730619</v>
+        <v>7.962109622638234</v>
       </c>
       <c r="H12" t="n">
-        <v>7.962109622638234</v>
+        <v>6.163348530881702</v>
       </c>
       <c r="I12" t="n">
-        <v>6.163348530881702</v>
+        <v>2.273165581775261</v>
       </c>
       <c r="J12" t="n">
-        <v>2.273165581775261</v>
+        <v>0.7741648995230374</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7741648995230374</v>
+        <v>0.7670525609111774</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7670525609111774</v>
+        <v>0.1132417654991327</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1132417654991327</v>
+        <v>0.05362842719167522</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05362842719167522</v>
+        <v>0.4387370161748747</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4387370161748747</v>
+        <v>1.762618467392699</v>
       </c>
       <c r="P12" t="n">
-        <v>1.762618467392699</v>
+        <v>1.717304219798767</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.717304219798767</v>
+        <v>1.562033532680399</v>
       </c>
       <c r="R12" t="n">
-        <v>1.562033532680399</v>
+        <v>1.777576338830109</v>
       </c>
       <c r="S12" t="n">
-        <v>1.777576338830109</v>
+        <v>2.15471022417047</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15471022417047</v>
+        <v>2.506479165258153</v>
       </c>
       <c r="U12" t="n">
-        <v>2.506479165258153</v>
+        <v>95.01678948910374</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>گلستان</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Golestan</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>829836.5116837677</v>
-      </c>
-      <c r="D13" t="n">
-        <v>20246559914.45267</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Golestan</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Golestan</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
           <t>27</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>25.65842729733427</v>
+      </c>
       <c r="G13" t="n">
-        <v>25.65842729733427</v>
+        <v>16.23217879671781</v>
       </c>
       <c r="H13" t="n">
-        <v>16.23217879671781</v>
+        <v>19.99086471190178</v>
       </c>
       <c r="I13" t="n">
-        <v>19.99086471190178</v>
+        <v>17.84973253293388</v>
       </c>
       <c r="J13" t="n">
-        <v>17.84973253293388</v>
+        <v>23.33698891901206</v>
       </c>
       <c r="K13" t="n">
-        <v>23.33698891901206</v>
+        <v>24.87666205627959</v>
       </c>
       <c r="L13" t="n">
-        <v>24.87666205627959</v>
+        <v>23.7508292862921</v>
       </c>
       <c r="M13" t="n">
-        <v>23.7508292862921</v>
+        <v>21.34501828226968</v>
       </c>
       <c r="N13" t="n">
-        <v>21.34501828226968</v>
+        <v>20.40618046196759</v>
       </c>
       <c r="O13" t="n">
-        <v>20.40618046196759</v>
+        <v>14.36506060209913</v>
       </c>
       <c r="P13" t="n">
-        <v>14.36506060209913</v>
+        <v>15.14602580868029</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.14602580868029</v>
+        <v>24.73836452660063</v>
       </c>
       <c r="R13" t="n">
-        <v>24.73836452660063</v>
+        <v>14.08864827278695</v>
       </c>
       <c r="S13" t="n">
-        <v>14.08864827278695</v>
+        <v>17.03253647968549</v>
       </c>
       <c r="T13" t="n">
-        <v>17.03253647968549</v>
+        <v>11.99440297073092</v>
       </c>
       <c r="U13" t="n">
-        <v>11.99440297073092</v>
+        <v>99.30775203930222</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>لرستان</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Lorestan</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>1165253.08135747</v>
-      </c>
-      <c r="D14" t="n">
-        <v>28063681239.42836</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lorestan</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lorestan</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
           <t>15</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>20.71425591116886</v>
+      </c>
       <c r="G14" t="n">
-        <v>20.71425591116886</v>
+        <v>10.73406534110862</v>
       </c>
       <c r="H14" t="n">
-        <v>10.73406534110862</v>
+        <v>9.228364276539271</v>
       </c>
       <c r="I14" t="n">
-        <v>9.228364276539271</v>
+        <v>9.156245013216857</v>
       </c>
       <c r="J14" t="n">
-        <v>9.156245013216857</v>
+        <v>11.85087739889179</v>
       </c>
       <c r="K14" t="n">
-        <v>11.85087739889179</v>
+        <v>10.06499438250761</v>
       </c>
       <c r="L14" t="n">
-        <v>10.06499438250761</v>
+        <v>8.98049275908566</v>
       </c>
       <c r="M14" t="n">
-        <v>8.98049275908566</v>
+        <v>7.027621560907738</v>
       </c>
       <c r="N14" t="n">
-        <v>7.027621560907738</v>
+        <v>8.350146027536622</v>
       </c>
       <c r="O14" t="n">
-        <v>8.350146027536622</v>
+        <v>12.4183318171909</v>
       </c>
       <c r="P14" t="n">
-        <v>12.4183318171909</v>
+        <v>13.87277481024849</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.87277481024849</v>
+        <v>11.63886327132367</v>
       </c>
       <c r="R14" t="n">
-        <v>11.63886327132367</v>
+        <v>11.24135829835569</v>
       </c>
       <c r="S14" t="n">
-        <v>11.24135829835569</v>
+        <v>6.527894088995525</v>
       </c>
       <c r="T14" t="n">
-        <v>6.527894088995525</v>
+        <v>19.1991058486579</v>
       </c>
       <c r="U14" t="n">
-        <v>19.1991058486579</v>
+        <v>98.15633677372033</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>مازندران</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Mazandaran</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>969597.831547944</v>
-      </c>
-      <c r="D15" t="n">
-        <v>23729691722.05499</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mazandaran</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mazandaran</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
           <t>02</t>
         </is>
       </c>
+      <c r="F15" t="n">
+        <v>18.47254313586624</v>
+      </c>
       <c r="G15" t="n">
-        <v>18.47254313586624</v>
+        <v>21.26791075742956</v>
       </c>
       <c r="H15" t="n">
-        <v>21.26791075742956</v>
+        <v>14.69944105825197</v>
       </c>
       <c r="I15" t="n">
-        <v>14.69944105825197</v>
+        <v>11.64749309062878</v>
       </c>
       <c r="J15" t="n">
-        <v>11.64749309062878</v>
+        <v>12.76801655157946</v>
       </c>
       <c r="K15" t="n">
-        <v>12.76801655157946</v>
+        <v>9.027827595413584</v>
       </c>
       <c r="L15" t="n">
-        <v>9.027827595413584</v>
+        <v>9.62914108001873</v>
       </c>
       <c r="M15" t="n">
-        <v>9.62914108001873</v>
+        <v>11.12558325938225</v>
       </c>
       <c r="N15" t="n">
-        <v>11.12558325938225</v>
+        <v>11.05750874781585</v>
       </c>
       <c r="O15" t="n">
-        <v>11.05750874781585</v>
+        <v>8.816148930648444</v>
       </c>
       <c r="P15" t="n">
-        <v>8.816148930648444</v>
+        <v>11.40998778315736</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.40998778315736</v>
+        <v>14.02940498843768</v>
       </c>
       <c r="R15" t="n">
-        <v>14.02940498843768</v>
+        <v>15.05218792549612</v>
       </c>
       <c r="S15" t="n">
-        <v>15.05218792549612</v>
+        <v>16.1978412992272</v>
       </c>
       <c r="T15" t="n">
-        <v>16.1978412992272</v>
+        <v>15.2532241191985</v>
       </c>
       <c r="U15" t="n">
-        <v>15.2532241191985</v>
+        <v>99.44165081365338</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>مرکزی</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Markazi</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>1111131.14216462</v>
-      </c>
-      <c r="D16" t="n">
-        <v>29026641895.09269</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Markazi</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Markazi</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
           <t>00</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>17.56662424557803</v>
+      </c>
       <c r="G16" t="n">
-        <v>17.56662424557803</v>
+        <v>13.16368779888057</v>
       </c>
       <c r="H16" t="n">
-        <v>13.16368779888057</v>
+        <v>9.97469162319131</v>
       </c>
       <c r="I16" t="n">
-        <v>9.97469162319131</v>
+        <v>15.01399826088616</v>
       </c>
       <c r="J16" t="n">
-        <v>15.01399826088616</v>
+        <v>15.57326421672457</v>
       </c>
       <c r="K16" t="n">
-        <v>15.57326421672457</v>
+        <v>10.33602513873777</v>
       </c>
       <c r="L16" t="n">
-        <v>10.33602513873777</v>
+        <v>5.4286729534085</v>
       </c>
       <c r="M16" t="n">
-        <v>5.4286729534085</v>
+        <v>9.047260972531937</v>
       </c>
       <c r="N16" t="n">
-        <v>9.047260972531937</v>
+        <v>6.468815407503399</v>
       </c>
       <c r="O16" t="n">
-        <v>6.468815407503399</v>
+        <v>7.325669724445729</v>
       </c>
       <c r="P16" t="n">
-        <v>7.325669724445729</v>
+        <v>7.262785674825831</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.262785674825831</v>
+        <v>7.937741917005589</v>
       </c>
       <c r="R16" t="n">
-        <v>7.937741917005589</v>
+        <v>7.667922903524947</v>
       </c>
       <c r="S16" t="n">
-        <v>7.667922903524947</v>
+        <v>9.169188813981226</v>
       </c>
       <c r="T16" t="n">
-        <v>9.169188813981226</v>
+        <v>7.740456025029233</v>
       </c>
       <c r="U16" t="n">
-        <v>7.740456025029233</v>
+        <v>99.70372594254654</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>ایلام</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Ilam</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>1083189.22271757</v>
-      </c>
-      <c r="D17" t="n">
-        <v>19698498142.11096</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ilam</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ilam</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
           <t>16</t>
         </is>
       </c>
+      <c r="F17" t="n">
+        <v>16.22986864441133</v>
+      </c>
       <c r="G17" t="n">
-        <v>16.22986864441133</v>
+        <v>5.359767822242444</v>
       </c>
       <c r="H17" t="n">
-        <v>5.359767822242444</v>
+        <v>2.020870005212266</v>
       </c>
       <c r="I17" t="n">
-        <v>2.020870005212266</v>
+        <v>2.116014175921601</v>
       </c>
       <c r="J17" t="n">
-        <v>2.116014175921601</v>
+        <v>7.027030090931956</v>
       </c>
       <c r="K17" t="n">
-        <v>7.027030090931956</v>
+        <v>4.677096579360915</v>
       </c>
       <c r="L17" t="n">
-        <v>4.677096579360915</v>
+        <v>4.783415216319405</v>
       </c>
       <c r="M17" t="n">
-        <v>4.783415216319405</v>
+        <v>4.088192242010246</v>
       </c>
       <c r="N17" t="n">
-        <v>4.088192242010246</v>
+        <v>6.464614866328176</v>
       </c>
       <c r="O17" t="n">
-        <v>6.464614866328176</v>
+        <v>3.099543854495249</v>
       </c>
       <c r="P17" t="n">
-        <v>3.099543854495249</v>
+        <v>3.509614455021046</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.509614455021046</v>
+        <v>3.466288131694262</v>
       </c>
       <c r="R17" t="n">
-        <v>3.466288131694262</v>
+        <v>3.266828530957659</v>
       </c>
       <c r="S17" t="n">
-        <v>3.266828530957659</v>
+        <v>2.390720978970417</v>
       </c>
       <c r="T17" t="n">
-        <v>2.390720978970417</v>
+        <v>1.897916457925739</v>
       </c>
       <c r="U17" t="n">
-        <v>1.897916457925739</v>
+        <v>99.51115072061762</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>خراسان شمالی</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Khorasan-e Shomali</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>853227.2276604956</v>
-      </c>
-      <c r="D18" t="n">
-        <v>28239620259.99553</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>North Khorasan</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>North Khorasan</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
           <t>28</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>17.11901084821293</v>
+      </c>
       <c r="G18" t="n">
-        <v>17.11901084821293</v>
+        <v>17.20833773295264</v>
       </c>
       <c r="H18" t="n">
-        <v>17.20833773295264</v>
+        <v>14.54488697414247</v>
       </c>
       <c r="I18" t="n">
-        <v>14.54488697414247</v>
+        <v>13.36260715413119</v>
       </c>
       <c r="J18" t="n">
-        <v>13.36260715413119</v>
+        <v>11.95948391309266</v>
       </c>
       <c r="K18" t="n">
-        <v>11.95948391309266</v>
+        <v>7.938153674203694</v>
       </c>
       <c r="L18" t="n">
-        <v>7.938153674203694</v>
+        <v>9.571647572198085</v>
       </c>
       <c r="M18" t="n">
-        <v>9.571647572198085</v>
+        <v>8.402986606050561</v>
       </c>
       <c r="N18" t="n">
-        <v>8.402986606050561</v>
+        <v>7.422845721841824</v>
       </c>
       <c r="O18" t="n">
-        <v>7.422845721841824</v>
+        <v>10.48325696361492</v>
       </c>
       <c r="P18" t="n">
-        <v>10.48325696361492</v>
+        <v>15.68571776209998</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.68571776209998</v>
+        <v>8.433046991604899</v>
       </c>
       <c r="R18" t="n">
-        <v>8.433046991604899</v>
+        <v>6.848301962094064</v>
       </c>
       <c r="S18" t="n">
-        <v>6.848301962094064</v>
+        <v>6.758905087390519</v>
       </c>
       <c r="T18" t="n">
-        <v>6.758905087390519</v>
+        <v>2.190644533074132</v>
       </c>
       <c r="U18" t="n">
-        <v>2.190644533074132</v>
+        <v>99.88515806332219</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>خراسان جنوبی</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Khorasan-e Jonubi</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1830202.677893837</v>
-      </c>
-      <c r="D19" t="n">
-        <v>148983066998.0802</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>South Khorasan</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>South Khorasan</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
           <t>29</t>
         </is>
       </c>
+      <c r="F19" t="n">
+        <v>15.54459011616227</v>
+      </c>
       <c r="G19" t="n">
-        <v>15.54459011616227</v>
+        <v>7.649666659374938</v>
       </c>
       <c r="H19" t="n">
-        <v>7.649666659374938</v>
+        <v>4.829833788959821</v>
       </c>
       <c r="I19" t="n">
-        <v>4.829833788959821</v>
+        <v>0.2341477651362529</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2341477651362529</v>
+        <v>3.253244814385872</v>
       </c>
       <c r="K19" t="n">
-        <v>3.253244814385872</v>
+        <v>4.304602777874742</v>
       </c>
       <c r="L19" t="n">
-        <v>4.304602777874742</v>
+        <v>4.281491532451831</v>
       </c>
       <c r="M19" t="n">
-        <v>4.281491532451831</v>
+        <v>6.755071427325531</v>
       </c>
       <c r="N19" t="n">
-        <v>6.755071427325531</v>
+        <v>6.974617065954404</v>
       </c>
       <c r="O19" t="n">
-        <v>6.974617065954404</v>
+        <v>4.514972916081847</v>
       </c>
       <c r="P19" t="n">
-        <v>4.514972916081847</v>
+        <v>4.115011879719924</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.115011879719924</v>
+        <v>3.82287906410811</v>
       </c>
       <c r="R19" t="n">
-        <v>3.82287906410811</v>
+        <v>3.265879891756664</v>
       </c>
       <c r="S19" t="n">
-        <v>3.265879891756664</v>
+        <v>1.549008959904554</v>
       </c>
       <c r="T19" t="n">
-        <v>1.549008959904554</v>
+        <v>0.6401765161723781</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6401765161723781</v>
+        <v>99.586194786207</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>کرمانشاه</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Kermanshah</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1119651.216249593</v>
-      </c>
-      <c r="D20" t="n">
-        <v>24991014922.21375</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Kermanshah</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kermanshah</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
           <t>05</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>10.55001218929782</v>
+      </c>
       <c r="G20" t="n">
-        <v>10.55001218929782</v>
+        <v>12.03645290495467</v>
       </c>
       <c r="H20" t="n">
-        <v>12.03645290495467</v>
+        <v>15.82879218721978</v>
       </c>
       <c r="I20" t="n">
-        <v>15.82879218721978</v>
+        <v>12.52123300639639</v>
       </c>
       <c r="J20" t="n">
-        <v>12.52123300639639</v>
+        <v>12.77927385420747</v>
       </c>
       <c r="K20" t="n">
-        <v>12.77927385420747</v>
+        <v>14.45386158823227</v>
       </c>
       <c r="L20" t="n">
-        <v>14.45386158823227</v>
+        <v>14.16611086815648</v>
       </c>
       <c r="M20" t="n">
-        <v>14.16611086815648</v>
+        <v>12.59045511890113</v>
       </c>
       <c r="N20" t="n">
-        <v>12.59045511890113</v>
+        <v>6.256104560421302</v>
       </c>
       <c r="O20" t="n">
-        <v>6.256104560421302</v>
+        <v>12.34968548160033</v>
       </c>
       <c r="P20" t="n">
-        <v>12.34968548160033</v>
+        <v>10.73510001447265</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.73510001447265</v>
+        <v>8.306290144319329</v>
       </c>
       <c r="R20" t="n">
-        <v>8.306290144319329</v>
+        <v>10.16925457807965</v>
       </c>
       <c r="S20" t="n">
-        <v>10.16925457807965</v>
+        <v>11.00710811480013</v>
       </c>
       <c r="T20" t="n">
-        <v>11.00710811480013</v>
+        <v>7.221638253077585</v>
       </c>
       <c r="U20" t="n">
-        <v>7.221638253077585</v>
+        <v>99.01489683155027</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>کرمان</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Kerman</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>2070342.027116081</v>
-      </c>
-      <c r="D21" t="n">
-        <v>179954825234.9203</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kerman</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerman</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
           <t>08</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>8.374309068643342</v>
+      </c>
       <c r="G21" t="n">
-        <v>8.374309068643342</v>
+        <v>7.602109683055687</v>
       </c>
       <c r="H21" t="n">
-        <v>7.602109683055687</v>
+        <v>9.066570728049099</v>
       </c>
       <c r="I21" t="n">
-        <v>9.066570728049099</v>
+        <v>7.656828665066488</v>
       </c>
       <c r="J21" t="n">
-        <v>7.656828665066488</v>
+        <v>5.251560876684165</v>
       </c>
       <c r="K21" t="n">
-        <v>5.251560876684165</v>
+        <v>7.980574548429114</v>
       </c>
       <c r="L21" t="n">
-        <v>7.980574548429114</v>
+        <v>19.19853514416969</v>
       </c>
       <c r="M21" t="n">
-        <v>19.19853514416969</v>
+        <v>19.81279673112052</v>
       </c>
       <c r="N21" t="n">
-        <v>19.81279673112052</v>
+        <v>22.47693841169259</v>
       </c>
       <c r="O21" t="n">
-        <v>22.47693841169259</v>
+        <v>19.73235968051396</v>
       </c>
       <c r="P21" t="n">
-        <v>19.73235968051396</v>
+        <v>13.31144787351886</v>
       </c>
       <c r="Q21" t="n">
-        <v>13.31144787351886</v>
+        <v>14.20406646948719</v>
       </c>
       <c r="R21" t="n">
-        <v>14.20406646948719</v>
+        <v>18.8166681483101</v>
       </c>
       <c r="S21" t="n">
-        <v>18.8166681483101</v>
+        <v>16.3351436255261</v>
       </c>
       <c r="T21" t="n">
-        <v>16.3351436255261</v>
+        <v>16.67709664859791</v>
       </c>
       <c r="U21" t="n">
-        <v>16.67709664859791</v>
+        <v>77.25709846199248</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>خراسان رضوی</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Khorasan-e Razavi</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>2010976.735971405</v>
-      </c>
-      <c r="D22" t="n">
-        <v>117727813990.9483</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Razavi Khorasan</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Razavi Khorasan</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
           <t>09</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>12.9443305528397</v>
+      </c>
       <c r="G22" t="n">
-        <v>12.9443305528397</v>
+        <v>7.004128390020424</v>
       </c>
       <c r="H22" t="n">
-        <v>7.004128390020424</v>
+        <v>9.203300004151075</v>
       </c>
       <c r="I22" t="n">
-        <v>9.203300004151075</v>
+        <v>9.586155671439272</v>
       </c>
       <c r="J22" t="n">
-        <v>9.586155671439272</v>
+        <v>9.780190130151226</v>
       </c>
       <c r="K22" t="n">
-        <v>9.780190130151226</v>
+        <v>9.634036011904213</v>
       </c>
       <c r="L22" t="n">
-        <v>9.634036011904213</v>
+        <v>10.39427762200415</v>
       </c>
       <c r="M22" t="n">
-        <v>10.39427762200415</v>
+        <v>13.2387937717469</v>
       </c>
       <c r="N22" t="n">
-        <v>13.2387937717469</v>
+        <v>12.56348268222129</v>
       </c>
       <c r="O22" t="n">
-        <v>12.56348268222129</v>
+        <v>12.61466107656021</v>
       </c>
       <c r="P22" t="n">
-        <v>12.61466107656021</v>
+        <v>15.63601233240557</v>
       </c>
       <c r="Q22" t="n">
-        <v>15.63601233240557</v>
+        <v>14.38373493271603</v>
       </c>
       <c r="R22" t="n">
-        <v>14.38373493271603</v>
+        <v>8.73379122939895</v>
       </c>
       <c r="S22" t="n">
-        <v>8.73379122939895</v>
+        <v>8.771829657478831</v>
       </c>
       <c r="T22" t="n">
-        <v>8.771829657478831</v>
+        <v>7.584980110171911</v>
       </c>
       <c r="U22" t="n">
-        <v>7.584980110171911</v>
+        <v>98.81057111686259</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>گیلان</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Gilan</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>707727.0693539027</v>
-      </c>
-      <c r="D23" t="n">
-        <v>14065157414.66251</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Gilan</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gilan</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
           <t>01</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>16.24323511687749</v>
+      </c>
       <c r="G23" t="n">
-        <v>16.24323511687749</v>
+        <v>14.0027345374162</v>
       </c>
       <c r="H23" t="n">
-        <v>14.0027345374162</v>
+        <v>13.89402970957715</v>
       </c>
       <c r="I23" t="n">
-        <v>13.89402970957715</v>
+        <v>11.85687401886255</v>
       </c>
       <c r="J23" t="n">
-        <v>11.85687401886255</v>
+        <v>14.68631875214007</v>
       </c>
       <c r="K23" t="n">
-        <v>14.68631875214007</v>
+        <v>16.15421983626184</v>
       </c>
       <c r="L23" t="n">
-        <v>16.15421983626184</v>
+        <v>13.89730449729396</v>
       </c>
       <c r="M23" t="n">
-        <v>13.89730449729396</v>
+        <v>14.9101170088044</v>
       </c>
       <c r="N23" t="n">
-        <v>14.9101170088044</v>
+        <v>13.61130571602486</v>
       </c>
       <c r="O23" t="n">
-        <v>13.61130571602486</v>
+        <v>12.26756333846978</v>
       </c>
       <c r="P23" t="n">
-        <v>12.26756333846978</v>
+        <v>12.11177740365711</v>
       </c>
       <c r="Q23" t="n">
-        <v>12.11177740365711</v>
+        <v>15.98382367716773</v>
       </c>
       <c r="R23" t="n">
-        <v>15.98382367716773</v>
+        <v>13.89993685458227</v>
       </c>
       <c r="S23" t="n">
-        <v>13.89993685458227</v>
+        <v>12.11688307035842</v>
       </c>
       <c r="T23" t="n">
-        <v>12.11688307035842</v>
+        <v>11.5967188117014</v>
       </c>
       <c r="U23" t="n">
-        <v>11.5967188117014</v>
+        <v>99.88033004405035</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>آذربایجان شرقی</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Azarbayejan-e Sharqi</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1272552.92514156</v>
-      </c>
-      <c r="D24" t="n">
-        <v>48043199156.76431</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>East Azerbaijan</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>East Azerbaijan</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
           <t>03</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>11.46483687537244</v>
+      </c>
       <c r="G24" t="n">
-        <v>11.46483687537244</v>
+        <v>27.78231060965273</v>
       </c>
       <c r="H24" t="n">
-        <v>27.78231060965273</v>
+        <v>18.09387508094609</v>
       </c>
       <c r="I24" t="n">
-        <v>18.09387508094609</v>
+        <v>16.20392251630901</v>
       </c>
       <c r="J24" t="n">
-        <v>16.20392251630901</v>
+        <v>18.40406686367454</v>
       </c>
       <c r="K24" t="n">
-        <v>18.40406686367454</v>
+        <v>15.58923722570786</v>
       </c>
       <c r="L24" t="n">
-        <v>15.58923722570786</v>
+        <v>13.27338346043497</v>
       </c>
       <c r="M24" t="n">
-        <v>13.27338346043497</v>
+        <v>8.327928219015499</v>
       </c>
       <c r="N24" t="n">
-        <v>8.327928219015499</v>
+        <v>8.080317139663673</v>
       </c>
       <c r="O24" t="n">
-        <v>8.080317139663673</v>
+        <v>9.134406641310976</v>
       </c>
       <c r="P24" t="n">
-        <v>9.134406641310976</v>
+        <v>11.10687787974955</v>
       </c>
       <c r="Q24" t="n">
-        <v>11.10687787974955</v>
+        <v>9.241883630872646</v>
       </c>
       <c r="R24" t="n">
-        <v>9.241883630872646</v>
+        <v>9.788437986126137</v>
       </c>
       <c r="S24" t="n">
-        <v>9.788437986126137</v>
+        <v>9.832529237576342</v>
       </c>
       <c r="T24" t="n">
-        <v>9.832529237576342</v>
+        <v>9.591606363798812</v>
       </c>
       <c r="U24" t="n">
-        <v>9.591606363798812</v>
+        <v>99.89249358230271</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>آذربایجان غربی</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Azarbayejan-e Gharbi</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1710275.012772338</v>
-      </c>
-      <c r="D25" t="n">
-        <v>39701480077.6248</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>West Azerbaijan</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Azerbaijan</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
           <t>04</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>11.70643855500209</v>
+      </c>
       <c r="G25" t="n">
-        <v>11.70643855500209</v>
+        <v>17.43621949399602</v>
       </c>
       <c r="H25" t="n">
-        <v>17.43621949399602</v>
+        <v>15.95806741043698</v>
       </c>
       <c r="I25" t="n">
-        <v>15.95806741043698</v>
+        <v>18.43012697712933</v>
       </c>
       <c r="J25" t="n">
-        <v>18.43012697712933</v>
+        <v>14.62673355942737</v>
       </c>
       <c r="K25" t="n">
-        <v>14.62673355942737</v>
+        <v>14.383105565941</v>
       </c>
       <c r="L25" t="n">
-        <v>14.383105565941</v>
+        <v>22.01535081014253</v>
       </c>
       <c r="M25" t="n">
-        <v>22.01535081014253</v>
+        <v>23.92953704220179</v>
       </c>
       <c r="N25" t="n">
-        <v>23.92953704220179</v>
+        <v>20.60021130119941</v>
       </c>
       <c r="O25" t="n">
-        <v>20.60021130119941</v>
+        <v>15.39940421591108</v>
       </c>
       <c r="P25" t="n">
-        <v>15.39940421591108</v>
+        <v>17.32834888558418</v>
       </c>
       <c r="Q25" t="n">
-        <v>17.32834888558418</v>
+        <v>14.75656455142232</v>
       </c>
       <c r="R25" t="n">
-        <v>14.75656455142232</v>
+        <v>19.01399193863356</v>
       </c>
       <c r="S25" t="n">
-        <v>19.01399193863356</v>
+        <v>30.50723687635899</v>
       </c>
       <c r="T25" t="n">
-        <v>30.50723687635899</v>
+        <v>21.56194786816691</v>
       </c>
       <c r="U25" t="n">
-        <v>21.56194786816691</v>
+        <v>94.79188053743057</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>اصفهان</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Esfahan</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1911347.881108768</v>
-      </c>
-      <c r="D26" t="n">
-        <v>106901555049.8287</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Esfahan</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Esfahan</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
           <t>10</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>10.56438346574383</v>
+      </c>
       <c r="G26" t="n">
-        <v>10.56438346574383</v>
+        <v>9.122560584739507</v>
       </c>
       <c r="H26" t="n">
-        <v>9.122560584739507</v>
+        <v>7.312682984461927</v>
       </c>
       <c r="I26" t="n">
-        <v>7.312682984461927</v>
+        <v>9.841375962643548</v>
       </c>
       <c r="J26" t="n">
-        <v>9.841375962643548</v>
+        <v>9.425371050427549</v>
       </c>
       <c r="K26" t="n">
-        <v>9.425371050427549</v>
+        <v>11.41531152655703</v>
       </c>
       <c r="L26" t="n">
-        <v>11.41531152655703</v>
+        <v>12.37682738921613</v>
       </c>
       <c r="M26" t="n">
-        <v>12.37682738921613</v>
+        <v>8.856278513747592</v>
       </c>
       <c r="N26" t="n">
-        <v>8.856278513747592</v>
+        <v>7.198219131339063</v>
       </c>
       <c r="O26" t="n">
-        <v>7.198219131339063</v>
+        <v>10.68565113017613</v>
       </c>
       <c r="P26" t="n">
-        <v>10.68565113017613</v>
+        <v>9.310111841597413</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.310111841597413</v>
+        <v>9.141335789196878</v>
       </c>
       <c r="R26" t="n">
-        <v>9.141335789196878</v>
+        <v>5.781167314657571</v>
       </c>
       <c r="S26" t="n">
-        <v>5.781167314657571</v>
+        <v>5.180166805084379</v>
       </c>
       <c r="T26" t="n">
-        <v>5.180166805084379</v>
+        <v>9.393164956025849</v>
       </c>
       <c r="U26" t="n">
-        <v>9.393164956025849</v>
+        <v>99.21515010632474</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>تهران</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Tehran</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>807328.6275577178</v>
-      </c>
-      <c r="D27" t="n">
-        <v>13604763682.53809</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tehran</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>23</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>9.891349133533591</v>
+      </c>
       <c r="G27" t="n">
-        <v>9.891349133533591</v>
+        <v>9.449480791377487</v>
       </c>
       <c r="H27" t="n">
-        <v>9.449480791377487</v>
+        <v>9.456497210626145</v>
       </c>
       <c r="I27" t="n">
-        <v>9.456497210626145</v>
+        <v>8.38985288581744</v>
       </c>
       <c r="J27" t="n">
-        <v>8.38985288581744</v>
+        <v>5.123271503477085</v>
       </c>
       <c r="K27" t="n">
-        <v>5.123271503477085</v>
+        <v>3.659699079832164</v>
       </c>
       <c r="L27" t="n">
-        <v>3.659699079832164</v>
+        <v>3.589167227807831</v>
       </c>
       <c r="M27" t="n">
-        <v>3.589167227807831</v>
+        <v>4.404020067808373</v>
       </c>
       <c r="N27" t="n">
-        <v>4.404020067808373</v>
+        <v>3.786221957728478</v>
       </c>
       <c r="O27" t="n">
-        <v>3.786221957728478</v>
+        <v>6.049687251521172</v>
       </c>
       <c r="P27" t="n">
-        <v>6.049687251521172</v>
+        <v>4.027112406890445</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.027112406890445</v>
+        <v>4.814340496253664</v>
       </c>
       <c r="R27" t="n">
-        <v>4.814340496253664</v>
+        <v>3.303653725627219</v>
       </c>
       <c r="S27" t="n">
-        <v>3.303653725627219</v>
+        <v>5.471041247315275</v>
       </c>
       <c r="T27" t="n">
-        <v>5.471041247315275</v>
+        <v>8.386398963967544</v>
       </c>
       <c r="U27" t="n">
-        <v>8.386398963967544</v>
+        <v>99.57144341022335</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>البرز</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Alborz</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>421112.372692363</v>
-      </c>
-      <c r="D28" t="n">
-        <v>5195845509.621514</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Alborz</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alborz</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
           <t>30</t>
         </is>
       </c>
+      <c r="F28" t="n">
+        <v>17.04599717054467</v>
+      </c>
       <c r="G28" t="n">
-        <v>17.04599717054467</v>
+        <v>8.342913795266147</v>
       </c>
       <c r="H28" t="n">
-        <v>8.342913795266147</v>
+        <v>8.613733377798297</v>
       </c>
       <c r="I28" t="n">
-        <v>8.613733377798297</v>
+        <v>4.13728139727051</v>
       </c>
       <c r="J28" t="n">
-        <v>4.13728139727051</v>
+        <v>1.871840413522068</v>
       </c>
       <c r="K28" t="n">
-        <v>1.871840413522068</v>
+        <v>3.177500407900542</v>
       </c>
       <c r="L28" t="n">
-        <v>3.177500407900542</v>
+        <v>6.632596361394443</v>
       </c>
       <c r="M28" t="n">
-        <v>6.632596361394443</v>
+        <v>4.041378982975756</v>
       </c>
       <c r="N28" t="n">
-        <v>4.041378982975756</v>
+        <v>3.939537282458599</v>
       </c>
       <c r="O28" t="n">
-        <v>3.939537282458599</v>
+        <v>4.695753062631032</v>
       </c>
       <c r="P28" t="n">
-        <v>4.695753062631032</v>
+        <v>3.732283107980071</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.732283107980071</v>
+        <v>3.861699122690416</v>
       </c>
       <c r="R28" t="n">
-        <v>3.861699122690416</v>
+        <v>5.170760297388713</v>
       </c>
       <c r="S28" t="n">
-        <v>5.170760297388713</v>
+        <v>4.023803077848864</v>
       </c>
       <c r="T28" t="n">
-        <v>4.023803077848864</v>
+        <v>1.964766092438264</v>
       </c>
       <c r="U28" t="n">
-        <v>1.964766092438264</v>
+        <v>99.81584030780411</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>هرمزگان</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Hormozgan</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>3072680.344416906</v>
-      </c>
-      <c r="D29" t="n">
-        <v>71397919976.965</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Hormozgan</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hormozgan</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
           <t>22</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>10.76005762571984</v>
+      </c>
       <c r="G29" t="n">
-        <v>10.76005762571984</v>
+        <v>1.545906156089259</v>
       </c>
       <c r="H29" t="n">
-        <v>1.545906156089259</v>
+        <v>2.411730016435307</v>
       </c>
       <c r="I29" t="n">
-        <v>2.411730016435307</v>
+        <v>4.63998900358331</v>
       </c>
       <c r="J29" t="n">
-        <v>4.63998900358331</v>
+        <v>8.754258416109478</v>
       </c>
       <c r="K29" t="n">
-        <v>8.754258416109478</v>
+        <v>7.460887088703498</v>
       </c>
       <c r="L29" t="n">
-        <v>7.460887088703498</v>
+        <v>5.584188055583113</v>
       </c>
       <c r="M29" t="n">
-        <v>5.584188055583113</v>
+        <v>9.402797410325896</v>
       </c>
       <c r="N29" t="n">
-        <v>9.402797410325896</v>
+        <v>8.498849953940702</v>
       </c>
       <c r="O29" t="n">
-        <v>8.498849953940702</v>
+        <v>8.751178244917122</v>
       </c>
       <c r="P29" t="n">
-        <v>8.751178244917122</v>
+        <v>16.25123198191224</v>
       </c>
       <c r="Q29" t="n">
-        <v>16.25123198191224</v>
+        <v>16.02228144264672</v>
       </c>
       <c r="R29" t="n">
-        <v>16.02228144264672</v>
+        <v>12.97272496688859</v>
       </c>
       <c r="S29" t="n">
-        <v>12.97272496688859</v>
+        <v>11.60333160113212</v>
       </c>
       <c r="T29" t="n">
-        <v>11.60333160113212</v>
+        <v>11.44583927677233</v>
       </c>
       <c r="U29" t="n">
-        <v>11.44583927677233</v>
+        <v>6.163010563129985</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>بوشهر</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Bushehr</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1343079.674420516</v>
-      </c>
-      <c r="D30" t="n">
-        <v>22962526589.13265</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bushehr</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bushehr</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
           <t>18</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>9.630185121083256</v>
+      </c>
       <c r="G30" t="n">
-        <v>9.630185121083256</v>
+        <v>7.288937680649638</v>
       </c>
       <c r="H30" t="n">
-        <v>7.288937680649638</v>
+        <v>18.75124898564892</v>
       </c>
       <c r="I30" t="n">
-        <v>18.75124898564892</v>
+        <v>8.041706917918944</v>
       </c>
       <c r="J30" t="n">
-        <v>8.041706917918944</v>
+        <v>7.835878909742244</v>
       </c>
       <c r="K30" t="n">
-        <v>7.835878909742244</v>
+        <v>11.80246200560098</v>
       </c>
       <c r="L30" t="n">
-        <v>11.80246200560098</v>
+        <v>15.29513809129406</v>
       </c>
       <c r="M30" t="n">
-        <v>15.29513809129406</v>
+        <v>13.08639867160497</v>
       </c>
       <c r="N30" t="n">
-        <v>13.08639867160497</v>
+        <v>13.35745414241529</v>
       </c>
       <c r="O30" t="n">
-        <v>13.35745414241529</v>
+        <v>11.94015540035137</v>
       </c>
       <c r="P30" t="n">
-        <v>11.94015540035137</v>
+        <v>8.860476413419329</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.860476413419329</v>
+        <v>10.01244780996343</v>
       </c>
       <c r="R30" t="n">
-        <v>10.01244780996343</v>
+        <v>9.283956597649865</v>
       </c>
       <c r="S30" t="n">
-        <v>9.283956597649865</v>
+        <v>9.419800987075613</v>
       </c>
       <c r="T30" t="n">
-        <v>9.419800987075613</v>
+        <v>9.843682716661032</v>
       </c>
       <c r="U30" t="n">
-        <v>9.843682716661032</v>
+        <v>80.37213329567395</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>فارس</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Fars</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1831886.811030366</v>
-      </c>
-      <c r="D31" t="n">
-        <v>122263876225.6777</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Fars</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fars</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
           <t>07</t>
         </is>
       </c>
+      <c r="F31" t="n">
+        <v>7.518799174276801</v>
+      </c>
       <c r="G31" t="n">
-        <v>7.518799174276801</v>
+        <v>8.595269865937547</v>
       </c>
       <c r="H31" t="n">
-        <v>8.595269865937547</v>
+        <v>6.705298756389677</v>
       </c>
       <c r="I31" t="n">
-        <v>6.705298756389677</v>
+        <v>8.097657845579882</v>
       </c>
       <c r="J31" t="n">
-        <v>8.097657845579882</v>
+        <v>7.621068184112836</v>
       </c>
       <c r="K31" t="n">
-        <v>7.621068184112836</v>
+        <v>5.08997926771158</v>
       </c>
       <c r="L31" t="n">
-        <v>5.08997926771158</v>
+        <v>7.312798428429113</v>
       </c>
       <c r="M31" t="n">
-        <v>7.312798428429113</v>
+        <v>5.526354247028796</v>
       </c>
       <c r="N31" t="n">
-        <v>5.526354247028796</v>
+        <v>5.550755823625056</v>
       </c>
       <c r="O31" t="n">
-        <v>5.550755823625056</v>
+        <v>7.627650063294405</v>
       </c>
       <c r="P31" t="n">
-        <v>7.627650063294405</v>
+        <v>7.222542579260595</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.222542579260595</v>
+        <v>7.481592836007287</v>
       </c>
       <c r="R31" t="n">
-        <v>7.481592836007287</v>
+        <v>9.431995351558733</v>
       </c>
       <c r="S31" t="n">
-        <v>9.431995351558733</v>
+        <v>8.657815079110083</v>
       </c>
       <c r="T31" t="n">
-        <v>8.657815079110083</v>
+        <v>7.775896371160044</v>
       </c>
       <c r="U31" t="n">
-        <v>7.775896371160044</v>
+        <v>95.59895369170516</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>خوزستان</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Khuzestan</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>2177338.704008521</v>
-      </c>
-      <c r="D32" t="n">
-        <v>63720006289.16002</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Khuzestan</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Khuzestan</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
           <t>06</t>
         </is>
       </c>
+      <c r="F32" t="n">
+        <v>8.475964984255304</v>
+      </c>
       <c r="G32" t="n">
-        <v>8.475964984255304</v>
+        <v>3.962112806688133</v>
       </c>
       <c r="H32" t="n">
-        <v>3.962112806688133</v>
+        <v>4.289874548303282</v>
       </c>
       <c r="I32" t="n">
-        <v>4.289874548303282</v>
+        <v>4.072956177904338</v>
       </c>
       <c r="J32" t="n">
-        <v>4.072956177904338</v>
+        <v>7.044826580058182</v>
       </c>
       <c r="K32" t="n">
-        <v>7.044826580058182</v>
+        <v>7.582440550149951</v>
       </c>
       <c r="L32" t="n">
-        <v>7.582440550149951</v>
+        <v>6.220779653905655</v>
       </c>
       <c r="M32" t="n">
-        <v>6.220779653905655</v>
+        <v>9.762708139710561</v>
       </c>
       <c r="N32" t="n">
-        <v>9.762708139710561</v>
+        <v>10.03272024746781</v>
       </c>
       <c r="O32" t="n">
-        <v>10.03272024746781</v>
+        <v>5.790886039743818</v>
       </c>
       <c r="P32" t="n">
-        <v>5.790886039743818</v>
+        <v>7.41004101540194</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.41004101540194</v>
+        <v>5.660272707544835</v>
       </c>
       <c r="R32" t="n">
-        <v>5.660272707544835</v>
+        <v>6.249444987983808</v>
       </c>
       <c r="S32" t="n">
-        <v>6.249444987983808</v>
+        <v>4.707011878536052</v>
       </c>
       <c r="T32" t="n">
-        <v>4.707011878536052</v>
+        <v>5.317883520350244</v>
       </c>
       <c r="U32" t="n">
-        <v>5.317883520350244</v>
+        <v>95.11843542860761</v>
       </c>
     </row>
   </sheetData>
